--- a/output/pdf_financials_xlsx/VCT.xlsx
+++ b/output/pdf_financials_xlsx/VCT.xlsx
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.006773</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.52626</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -12652,7 +12652,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
         <v>-1.006773</v>
       </c>

--- a/output/pdf_financials_xlsx/VCT.xlsx
+++ b/output/pdf_financials_xlsx/VCT.xlsx
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000478</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000713</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1268,13 +1268,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.719844</v>
+        <v>-1.719873</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.187642</v>
+        <v>-2.18812</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.831744</v>
+        <v>-0.832457</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.07382</v>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.719844</v>
+        <v>-1.719873</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.187642</v>
+        <v>-2.18812</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.831744</v>
+        <v>-0.832457</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.07382</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-24569200</v>
+        <v>-24569614.28571429</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-535.0458580967055</v>
+        <v>-535.1627656712402</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.141996</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.072088</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.141996</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.072088</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">
